--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs - VENTAS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2703" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7604293F-6F70-43C9-8BA4-0D0DB3B04394}"/>
+  <xr:revisionPtr revIDLastSave="2713" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7916B2B-F9C8-4CA4-B10D-AAD7511963B1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja2" sheetId="7" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$6341</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$6343</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9778" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9786" uniqueCount="94">
   <si>
     <t>Sucursal</t>
   </si>
@@ -694,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14AE435F-C8B7-4B0C-8617-5994DE6D3EA0}">
-  <dimension ref="A1:H6351"/>
+  <dimension ref="A1:H6353"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -58817,28 +58817,28 @@
     </row>
     <row r="2236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2236" s="2">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="B2236" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C2236">
-        <v>1017283114</v>
+        <v>431140540</v>
       </c>
       <c r="D2236" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E2236" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2236" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G2236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2236">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2237" spans="1:8" x14ac:dyDescent="0.25">
@@ -58858,13 +58858,13 @@
         <v>63</v>
       </c>
       <c r="F2237" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2237">
         <v>1</v>
       </c>
       <c r="H2237">
-        <v>36.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2238" spans="1:8" x14ac:dyDescent="0.25">
@@ -58884,18 +58884,18 @@
         <v>63</v>
       </c>
       <c r="F2238" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2238">
         <v>1</v>
       </c>
       <c r="H2238">
-        <v>1</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="2239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2239" s="2">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B2239" t="s">
         <v>40</v>
@@ -58916,7 +58916,7 @@
         <v>1</v>
       </c>
       <c r="H2239">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2240" spans="1:8" x14ac:dyDescent="0.25">
@@ -58942,24 +58942,24 @@
         <v>1</v>
       </c>
       <c r="H2240">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2241" s="2">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B2241" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C2241">
-        <v>438075071</v>
+        <v>1017283114</v>
       </c>
       <c r="D2241" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E2241" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2241" t="s">
         <v>69</v>
@@ -58968,21 +58968,21 @@
         <v>1</v>
       </c>
       <c r="H2241">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2242" s="2">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="B2242" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="C2242">
-        <v>431140540</v>
+        <v>438075071</v>
       </c>
       <c r="D2242" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E2242" t="s">
         <v>62</v>
@@ -58999,16 +58999,16 @@
     </row>
     <row r="2243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2243" s="2">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="B2243" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C2243">
-        <v>10171674991</v>
+        <v>431140540</v>
       </c>
       <c r="D2243" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E2243" t="s">
         <v>62</v>
@@ -59020,47 +59020,47 @@
         <v>1</v>
       </c>
       <c r="H2243">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2244" s="2">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="B2244" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2244">
+        <v>10171674991</v>
+      </c>
+      <c r="D2244" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2244" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2244" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2244">
+        <v>1</v>
+      </c>
+      <c r="H2244">
         <v>2</v>
-      </c>
-      <c r="C2244">
-        <v>1036689035</v>
-      </c>
-      <c r="D2244" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2244" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2244" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2244">
-        <v>1</v>
-      </c>
-      <c r="H2244">
-        <v>13.9</v>
       </c>
     </row>
     <row r="2245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2245" s="2">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B2245" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C2245">
-        <v>1040511721</v>
+        <v>1036689035</v>
       </c>
       <c r="D2245" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="E2245" t="s">
         <v>63</v>
@@ -59072,47 +59072,47 @@
         <v>1</v>
       </c>
       <c r="H2245">
-        <v>9.6999999999999993</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="2246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2246" s="2">
-        <v>46184</v>
+        <v>46178</v>
       </c>
       <c r="B2246" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C2246">
-        <v>1001547741</v>
+        <v>1040511721</v>
       </c>
       <c r="D2246" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="E2246" t="s">
         <v>63</v>
       </c>
       <c r="F2246" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2246">
         <v>1</v>
       </c>
       <c r="H2246">
-        <v>1</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="2247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2247" s="2">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="B2247" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C2247">
-        <v>1128483659</v>
+        <v>1001547741</v>
       </c>
       <c r="D2247" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E2247" t="s">
         <v>63</v>
@@ -59124,24 +59124,24 @@
         <v>1</v>
       </c>
       <c r="H2247">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2248" s="2">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B2248" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C2248">
-        <v>432553771</v>
+        <v>1128483659</v>
       </c>
       <c r="D2248" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="E2248" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2248" t="s">
         <v>69</v>
@@ -59150,102 +59150,102 @@
         <v>1</v>
       </c>
       <c r="H2248">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2249" s="2">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B2249" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C2249">
-        <v>431140540</v>
+        <v>432553771</v>
       </c>
       <c r="D2249" t="s">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="E2249" t="s">
         <v>62</v>
       </c>
       <c r="F2249" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2249">
         <v>1</v>
       </c>
       <c r="H2249">
-        <v>14.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2250" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B2250" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C2250">
-        <v>1000922411</v>
+        <v>431140540</v>
       </c>
       <c r="D2250" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E2250" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2250" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2250">
         <v>1</v>
       </c>
       <c r="H2250">
-        <v>3</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="2251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2251" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B2251" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C2251">
-        <v>1040516819</v>
+        <v>1000922411</v>
       </c>
       <c r="D2251" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E2251" t="s">
         <v>63</v>
       </c>
       <c r="F2251" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2251">
         <v>1</v>
       </c>
       <c r="H2251">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2252" s="2">
-        <v>46179</v>
+        <v>46184</v>
       </c>
       <c r="B2252" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C2252">
-        <v>10352328141</v>
+        <v>1040516819</v>
       </c>
       <c r="D2252" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E2252" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2252" t="s">
         <v>68</v>
@@ -59254,76 +59254,76 @@
         <v>1</v>
       </c>
       <c r="H2252">
-        <v>12.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2253" s="2">
-        <v>46174</v>
+        <v>46179</v>
       </c>
       <c r="B2253" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="C2253">
-        <v>1020401814</v>
+        <v>10352328141</v>
       </c>
       <c r="D2253" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="E2253" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2253" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2253">
         <v>1</v>
       </c>
       <c r="H2253">
-        <v>3</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="2254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2254" s="2">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="B2254" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C2254">
-        <v>10427737531</v>
+        <v>1020401814</v>
       </c>
       <c r="D2254" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="E2254" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2254" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2254">
         <v>1</v>
       </c>
       <c r="H2254">
-        <v>15.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2255" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B2255" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C2255">
-        <v>1037603803</v>
+        <v>10427737531</v>
       </c>
       <c r="D2255" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="E2255" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2255" t="s">
         <v>68</v>
@@ -59332,21 +59332,21 @@
         <v>1</v>
       </c>
       <c r="H2255">
-        <v>22.400000000000002</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="2256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2256" s="2">
-        <v>46179</v>
+        <v>46184</v>
       </c>
       <c r="B2256" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C2256">
-        <v>1039679117</v>
+        <v>1037603803</v>
       </c>
       <c r="D2256" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="E2256" t="s">
         <v>63</v>
@@ -59358,151 +59358,151 @@
         <v>1</v>
       </c>
       <c r="H2256">
-        <v>36.4</v>
+        <v>22.400000000000002</v>
       </c>
     </row>
     <row r="2257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2257" s="2">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B2257" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C2257">
-        <v>431140540</v>
+        <v>1039679117</v>
       </c>
       <c r="D2257" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="E2257" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2257" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2257">
         <v>1</v>
       </c>
       <c r="H2257">
-        <v>1</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="2258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2258" s="2">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="B2258" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="C2258">
-        <v>11284649230</v>
+        <v>431140540</v>
       </c>
       <c r="D2258" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E2258" t="s">
         <v>62</v>
       </c>
       <c r="F2258" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2258">
         <v>1</v>
       </c>
       <c r="H2258">
-        <v>11.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2259" s="2">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="B2259" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="C2259">
-        <v>1026145688</v>
+        <v>11284649230</v>
       </c>
       <c r="D2259" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E2259" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2259" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2259">
         <v>1</v>
       </c>
       <c r="H2259">
-        <v>1.5</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="2260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2260" s="2">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="B2260" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C2260">
-        <v>1036689035</v>
+        <v>1026145688</v>
       </c>
       <c r="D2260" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="E2260" t="s">
         <v>63</v>
       </c>
       <c r="F2260" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G2260">
         <v>1</v>
       </c>
       <c r="H2260">
-        <v>4.9800000000000004</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2261" s="2">
-        <v>46184</v>
+        <v>46179</v>
       </c>
       <c r="B2261" t="s">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="C2261">
-        <v>10171674991</v>
+        <v>1036689035</v>
       </c>
       <c r="D2261" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E2261" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2261" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2261">
         <v>1</v>
       </c>
       <c r="H2261">
-        <v>1</v>
+        <v>4.9800000000000004</v>
       </c>
     </row>
     <row r="2262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2262" s="2">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B2262" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C2262">
-        <v>431140540</v>
+        <v>10171674991</v>
       </c>
       <c r="D2262" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E2262" t="s">
         <v>62</v>
@@ -59519,71 +59519,71 @@
     </row>
     <row r="2263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2263" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B2263" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C2263">
-        <v>10375445591</v>
+        <v>431140540</v>
       </c>
       <c r="D2263" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E2263" t="s">
         <v>62</v>
       </c>
       <c r="F2263" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G2263">
         <v>1</v>
       </c>
       <c r="H2263">
-        <v>13.57</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2264" s="2">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B2264" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C2264">
-        <v>1039597884</v>
+        <v>10375445591</v>
       </c>
       <c r="D2264" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="E2264" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2264" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2264">
         <v>1</v>
       </c>
       <c r="H2264">
-        <v>2</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="2265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2265" s="2">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B2265" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C2265">
-        <v>432553771</v>
+        <v>1039597884</v>
       </c>
       <c r="D2265" t="s">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="E2265" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2265" t="s">
         <v>69</v>
@@ -59592,38 +59592,38 @@
         <v>1</v>
       </c>
       <c r="H2265">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2266" s="2">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B2266" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C2266">
-        <v>432553771</v>
+        <v>1039597884</v>
       </c>
       <c r="D2266" t="s">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="E2266" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2266" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G2266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2266">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2267" s="2">
-        <v>46184</v>
+        <v>46175</v>
       </c>
       <c r="B2267" t="s">
         <v>50</v>
@@ -59649,19 +59649,19 @@
     </row>
     <row r="2268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2268" s="2">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="B2268" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C2268">
-        <v>43264120</v>
+        <v>432553771</v>
       </c>
       <c r="D2268" t="s">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="E2268" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2268" t="s">
         <v>69</v>
@@ -59670,24 +59670,24 @@
         <v>1</v>
       </c>
       <c r="H2268">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2269" s="2">
-        <v>46175</v>
+        <v>46184</v>
       </c>
       <c r="B2269" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C2269">
-        <v>43264120</v>
+        <v>432553771</v>
       </c>
       <c r="D2269" t="s">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="E2269" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2269" t="s">
         <v>69</v>
@@ -59701,16 +59701,16 @@
     </row>
     <row r="2270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2270" s="2">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="B2270" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C2270">
-        <v>43262406</v>
+        <v>43264120</v>
       </c>
       <c r="D2270" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="E2270" t="s">
         <v>63</v>
@@ -59722,24 +59722,24 @@
         <v>1</v>
       </c>
       <c r="H2270">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2271" s="2">
-        <v>46179</v>
+        <v>46175</v>
       </c>
       <c r="B2271" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2271">
-        <v>432786341</v>
+        <v>43264120</v>
       </c>
       <c r="D2271" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="E2271" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2271" t="s">
         <v>69</v>
@@ -59753,45 +59753,45 @@
     </row>
     <row r="2272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2272" s="2">
-        <v>46179</v>
+        <v>46174</v>
       </c>
       <c r="B2272" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C2272">
-        <v>432786341</v>
+        <v>43262406</v>
       </c>
       <c r="D2272" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E2272" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2272" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G2272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2272">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2273" s="2">
-        <v>46182</v>
+        <v>46179</v>
       </c>
       <c r="B2273" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C2273">
-        <v>1000922411</v>
+        <v>432786341</v>
       </c>
       <c r="D2273" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E2273" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2273" t="s">
         <v>69</v>
@@ -59800,38 +59800,38 @@
         <v>1</v>
       </c>
       <c r="H2273">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2274" s="2">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B2274" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2274">
-        <v>43264120</v>
+        <v>432786341</v>
       </c>
       <c r="D2274" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E2274" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2274" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G2274">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2274">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2275" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B2275" t="s">
         <v>32</v>
@@ -59857,16 +59857,16 @@
     </row>
     <row r="2276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2276" s="2">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B2276" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C2276">
-        <v>1128483659</v>
+        <v>43264120</v>
       </c>
       <c r="D2276" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E2276" t="s">
         <v>63</v>
@@ -59878,163 +59878,163 @@
         <v>1</v>
       </c>
       <c r="H2276">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2277" s="2">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B2277" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C2277">
-        <v>43262406</v>
+        <v>1000922411</v>
       </c>
       <c r="D2277" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E2277" t="s">
         <v>63</v>
       </c>
       <c r="F2277" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2277">
         <v>1</v>
       </c>
       <c r="H2277">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2278" s="2">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="B2278" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C2278">
-        <v>432786341</v>
+        <v>1128483659</v>
       </c>
       <c r="D2278" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="E2278" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2278" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2278">
         <v>1</v>
       </c>
       <c r="H2278">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2279" s="2">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="B2279" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C2279">
-        <v>1037603803</v>
+        <v>43262406</v>
       </c>
       <c r="D2279" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="E2279" t="s">
         <v>63</v>
       </c>
       <c r="F2279" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2279">
         <v>1</v>
       </c>
       <c r="H2279">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2280" s="2">
-        <v>46183</v>
+        <v>46175</v>
       </c>
       <c r="B2280" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C2280">
-        <v>1039597884</v>
+        <v>432786341</v>
       </c>
       <c r="D2280" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E2280" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2280" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2280">
         <v>1</v>
       </c>
       <c r="H2280">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="2281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2281" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B2281" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C2281">
-        <v>438075071</v>
+        <v>1037603803</v>
       </c>
       <c r="D2281" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E2281" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2281" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G2281">
         <v>1</v>
       </c>
       <c r="H2281">
-        <v>24.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2282" s="2">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B2282" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C2282">
-        <v>1026145688</v>
+        <v>1039597884</v>
       </c>
       <c r="D2282" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="E2282" t="s">
         <v>63</v>
       </c>
       <c r="F2282" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G2282">
         <v>1</v>
       </c>
       <c r="H2282">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2283" spans="1:8" x14ac:dyDescent="0.25">
@@ -60042,16 +60042,16 @@
         <v>46183</v>
       </c>
       <c r="B2283" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="C2283">
-        <v>43262406</v>
+        <v>438075071</v>
       </c>
       <c r="D2283" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E2283" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2283" t="s">
         <v>67</v>
@@ -60060,21 +60060,21 @@
         <v>1</v>
       </c>
       <c r="H2283">
-        <v>22.6</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="2284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2284" s="2">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="B2284" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="C2284">
-        <v>1017283114</v>
+        <v>1026145688</v>
       </c>
       <c r="D2284" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="E2284" t="s">
         <v>63</v>
@@ -60086,21 +60086,21 @@
         <v>1</v>
       </c>
       <c r="H2284">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2285" s="2">
-        <v>46174</v>
+        <v>46183</v>
       </c>
       <c r="B2285" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C2285">
-        <v>1039679117</v>
+        <v>43262406</v>
       </c>
       <c r="D2285" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="E2285" t="s">
         <v>63</v>
@@ -60112,21 +60112,21 @@
         <v>1</v>
       </c>
       <c r="H2285">
-        <v>21</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="2286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2286" s="2">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="B2286" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C2286">
-        <v>1040759381</v>
+        <v>1017283114</v>
       </c>
       <c r="D2286" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E2286" t="s">
         <v>63</v>
@@ -60138,21 +60138,21 @@
         <v>1</v>
       </c>
       <c r="H2286">
-        <v>22.6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2287" s="2">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B2287" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C2287">
-        <v>1017284920</v>
+        <v>1039679117</v>
       </c>
       <c r="D2287" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E2287" t="s">
         <v>63</v>
@@ -60164,21 +60164,21 @@
         <v>1</v>
       </c>
       <c r="H2287">
-        <v>22.6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2288" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B2288" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C2288">
-        <v>1017284920</v>
+        <v>1040759381</v>
       </c>
       <c r="D2288" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="E2288" t="s">
         <v>63</v>
@@ -60190,21 +60190,21 @@
         <v>1</v>
       </c>
       <c r="H2288">
-        <v>16</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="2289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2289" s="2">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="B2289" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C2289">
-        <v>1040759381</v>
+        <v>1017284920</v>
       </c>
       <c r="D2289" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="E2289" t="s">
         <v>63</v>
@@ -60216,24 +60216,24 @@
         <v>1</v>
       </c>
       <c r="H2289">
-        <v>21</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="2290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2290" s="2">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="B2290" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C2290">
-        <v>31274520</v>
+        <v>1017284920</v>
       </c>
       <c r="D2290" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E2290" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2290" t="s">
         <v>67</v>
@@ -60242,7 +60242,7 @@
         <v>1</v>
       </c>
       <c r="H2290">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2291" spans="1:8" x14ac:dyDescent="0.25">
@@ -60250,13 +60250,13 @@
         <v>46182</v>
       </c>
       <c r="B2291" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="C2291">
-        <v>43262406</v>
+        <v>1040759381</v>
       </c>
       <c r="D2291" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E2291" t="s">
         <v>63</v>
@@ -60268,7 +60268,7 @@
         <v>1</v>
       </c>
       <c r="H2291">
-        <v>22.6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2292" spans="1:8" x14ac:dyDescent="0.25">
@@ -60299,16 +60299,16 @@
     </row>
     <row r="2293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2293" s="2">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="B2293" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C2293">
-        <v>1192897</v>
+        <v>43262406</v>
       </c>
       <c r="D2293" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E2293" t="s">
         <v>63</v>
@@ -60320,7 +60320,7 @@
         <v>1</v>
       </c>
       <c r="H2293">
-        <v>16</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="2294" spans="1:8" x14ac:dyDescent="0.25">
@@ -60328,13 +60328,13 @@
         <v>46177</v>
       </c>
       <c r="B2294" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C2294">
-        <v>10427737531</v>
+        <v>31274520</v>
       </c>
       <c r="D2294" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="E2294" t="s">
         <v>62</v>
@@ -60346,21 +60346,21 @@
         <v>1</v>
       </c>
       <c r="H2294">
-        <v>8.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2295" s="2">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="B2295" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C2295">
-        <v>1036689035</v>
+        <v>1192897</v>
       </c>
       <c r="D2295" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="E2295" t="s">
         <v>63</v>
@@ -60372,24 +60372,24 @@
         <v>1</v>
       </c>
       <c r="H2295">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2296" s="2">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="B2296" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C2296">
-        <v>43262406</v>
+        <v>10427737531</v>
       </c>
       <c r="D2296" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E2296" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2296" t="s">
         <v>67</v>
@@ -60398,21 +60398,21 @@
         <v>1</v>
       </c>
       <c r="H2296">
-        <v>21</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="2297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2297" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B2297" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C2297">
-        <v>1128483659</v>
+        <v>1036689035</v>
       </c>
       <c r="D2297" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="E2297" t="s">
         <v>63</v>
@@ -60424,21 +60424,21 @@
         <v>1</v>
       </c>
       <c r="H2297">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2298" s="2">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="B2298" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C2298">
-        <v>1001547741</v>
+        <v>43262406</v>
       </c>
       <c r="D2298" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E2298" t="s">
         <v>63</v>
@@ -60450,21 +60450,21 @@
         <v>1</v>
       </c>
       <c r="H2298">
-        <v>8.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2299" s="2">
-        <v>46175</v>
+        <v>46184</v>
       </c>
       <c r="B2299" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C2299">
-        <v>1001547741</v>
+        <v>1128483659</v>
       </c>
       <c r="D2299" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="E2299" t="s">
         <v>63</v>
@@ -60476,24 +60476,24 @@
         <v>1</v>
       </c>
       <c r="H2299">
-        <v>8.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2300" s="2">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B2300" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C2300">
-        <v>432553771</v>
+        <v>1001547741</v>
       </c>
       <c r="D2300" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="E2300" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2300" t="s">
         <v>67</v>
@@ -60502,21 +60502,21 @@
         <v>1</v>
       </c>
       <c r="H2300">
-        <v>22.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="2301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2301" s="2">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="B2301" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C2301">
-        <v>1128483659</v>
+        <v>1001547741</v>
       </c>
       <c r="D2301" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E2301" t="s">
         <v>63</v>
@@ -60528,21 +60528,21 @@
         <v>1</v>
       </c>
       <c r="H2301">
-        <v>21</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="2302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2302" s="2">
-        <v>46184</v>
+        <v>46176</v>
       </c>
       <c r="B2302" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C2302">
-        <v>10375445591</v>
+        <v>432553771</v>
       </c>
       <c r="D2302" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E2302" t="s">
         <v>62</v>
@@ -60554,21 +60554,21 @@
         <v>1</v>
       </c>
       <c r="H2302">
-        <v>7.25</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="2303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2303" s="2">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="B2303" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C2303">
-        <v>1036689035</v>
+        <v>1128483659</v>
       </c>
       <c r="D2303" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E2303" t="s">
         <v>63</v>
@@ -60580,24 +60580,24 @@
         <v>1</v>
       </c>
       <c r="H2303">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2304" s="2">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="B2304" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C2304">
-        <v>1192897</v>
+        <v>10375445591</v>
       </c>
       <c r="D2304" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E2304" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2304" t="s">
         <v>67</v>
@@ -60606,7 +60606,7 @@
         <v>1</v>
       </c>
       <c r="H2304">
-        <v>22.6</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="2305" spans="1:8" x14ac:dyDescent="0.25">
@@ -60614,13 +60614,13 @@
         <v>46174</v>
       </c>
       <c r="B2305" t="s">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="C2305">
-        <v>1037603803</v>
+        <v>1036689035</v>
       </c>
       <c r="D2305" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="E2305" t="s">
         <v>63</v>
@@ -60637,16 +60637,16 @@
     </row>
     <row r="2306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2306" s="2">
-        <v>46184</v>
+        <v>46177</v>
       </c>
       <c r="B2306" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C2306">
-        <v>1036689035</v>
+        <v>1192897</v>
       </c>
       <c r="D2306" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="E2306" t="s">
         <v>63</v>
@@ -60658,21 +60658,21 @@
         <v>1</v>
       </c>
       <c r="H2306">
-        <v>24</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="2307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2307" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B2307" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C2307">
-        <v>1007471096</v>
+        <v>1037603803</v>
       </c>
       <c r="D2307" t="s">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="E2307" t="s">
         <v>63</v>
@@ -60684,24 +60684,24 @@
         <v>1</v>
       </c>
       <c r="H2307">
-        <v>8.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2308" s="2">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B2308" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C2308">
-        <v>11284350761</v>
+        <v>1036689035</v>
       </c>
       <c r="D2308" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E2308" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2308" t="s">
         <v>67</v>
@@ -60710,24 +60710,24 @@
         <v>1</v>
       </c>
       <c r="H2308">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2309" s="2">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B2309" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C2309">
-        <v>438075071</v>
+        <v>1007471096</v>
       </c>
       <c r="D2309" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="E2309" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2309" t="s">
         <v>67</v>
@@ -60736,21 +60736,21 @@
         <v>1</v>
       </c>
       <c r="H2309">
-        <v>21</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2310" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B2310" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C2310">
-        <v>10386260211</v>
+        <v>11284350761</v>
       </c>
       <c r="D2310" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E2310" t="s">
         <v>62</v>
@@ -60767,19 +60767,19 @@
     </row>
     <row r="2311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2311" s="2">
-        <v>46183</v>
+        <v>46176</v>
       </c>
       <c r="B2311" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="C2311">
-        <v>1001547741</v>
+        <v>438075071</v>
       </c>
       <c r="D2311" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="E2311" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2311" t="s">
         <v>67</v>
@@ -60788,7 +60788,7 @@
         <v>1</v>
       </c>
       <c r="H2311">
-        <v>8.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2312" spans="1:8" x14ac:dyDescent="0.25">
@@ -60796,16 +60796,16 @@
         <v>46184</v>
       </c>
       <c r="B2312" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C2312">
-        <v>43264120</v>
+        <v>10386260211</v>
       </c>
       <c r="D2312" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E2312" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2312" t="s">
         <v>67</v>
@@ -60814,21 +60814,21 @@
         <v>1</v>
       </c>
       <c r="H2312">
-        <v>22.6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2313" s="2">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B2313" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C2313">
-        <v>1040759381</v>
+        <v>1001547741</v>
       </c>
       <c r="D2313" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="E2313" t="s">
         <v>63</v>
@@ -60840,24 +60840,24 @@
         <v>1</v>
       </c>
       <c r="H2313">
-        <v>22.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="2314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2314" s="2">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B2314" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="C2314">
-        <v>11284649230</v>
+        <v>43264120</v>
       </c>
       <c r="D2314" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E2314" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2314" t="s">
         <v>67</v>
@@ -60866,21 +60866,21 @@
         <v>1</v>
       </c>
       <c r="H2314">
-        <v>21</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2315" s="2">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="B2315" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2315">
-        <v>1039679117</v>
+        <v>1040759381</v>
       </c>
       <c r="D2315" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="E2315" t="s">
         <v>63</v>
@@ -60897,19 +60897,19 @@
     </row>
     <row r="2316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2316" s="2">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B2316" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="C2316">
-        <v>43629101</v>
+        <v>11284649230</v>
       </c>
       <c r="D2316" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="E2316" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2316" t="s">
         <v>67</v>
@@ -60923,16 +60923,16 @@
     </row>
     <row r="2317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2317" s="2">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B2317" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C2317">
-        <v>43264120</v>
+        <v>1039679117</v>
       </c>
       <c r="D2317" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E2317" t="s">
         <v>63</v>
@@ -60944,21 +60944,21 @@
         <v>1</v>
       </c>
       <c r="H2317">
-        <v>24.9</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="2318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2318" s="2">
-        <v>46184</v>
+        <v>46177</v>
       </c>
       <c r="B2318" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C2318">
-        <v>1001547741</v>
+        <v>43629101</v>
       </c>
       <c r="D2318" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="E2318" t="s">
         <v>63</v>
@@ -60970,12 +60970,12 @@
         <v>1</v>
       </c>
       <c r="H2318">
-        <v>8.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2319" s="2">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="B2319" t="s">
         <v>44</v>
@@ -60996,21 +60996,21 @@
         <v>1</v>
       </c>
       <c r="H2319">
-        <v>22.6</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="2320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2320" s="2">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B2320" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2320">
-        <v>1000444316</v>
+        <v>1001547741</v>
       </c>
       <c r="D2320" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E2320" t="s">
         <v>63</v>
@@ -61022,24 +61022,24 @@
         <v>1</v>
       </c>
       <c r="H2320">
-        <v>21</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="2321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2321" s="2">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="B2321" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2321">
-        <v>10384803501</v>
+        <v>43264120</v>
       </c>
       <c r="D2321" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="E2321" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2321" t="s">
         <v>67</v>
@@ -61048,21 +61048,21 @@
         <v>1</v>
       </c>
       <c r="H2321">
-        <v>8.5</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="2322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2322" s="2">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="B2322" t="s">
         <v>44</v>
       </c>
       <c r="C2322">
-        <v>1037603803</v>
+        <v>1000444316</v>
       </c>
       <c r="D2322" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="E2322" t="s">
         <v>63</v>
@@ -61074,24 +61074,24 @@
         <v>1</v>
       </c>
       <c r="H2322">
-        <v>22.6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2323" s="2">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B2323" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C2323">
-        <v>1042774546</v>
+        <v>10384803501</v>
       </c>
       <c r="D2323" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E2323" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2323" t="s">
         <v>67</v>
@@ -61100,12 +61100,12 @@
         <v>1</v>
       </c>
       <c r="H2323">
-        <v>16</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="2324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2324" s="2">
-        <v>46177</v>
+        <v>46174</v>
       </c>
       <c r="B2324" t="s">
         <v>44</v>
@@ -61126,21 +61126,21 @@
         <v>1</v>
       </c>
       <c r="H2324">
-        <v>21</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="2325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2325" s="2">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="B2325" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C2325">
-        <v>1026145688</v>
+        <v>1042774546</v>
       </c>
       <c r="D2325" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E2325" t="s">
         <v>63</v>
@@ -61152,21 +61152,21 @@
         <v>1</v>
       </c>
       <c r="H2325">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2326" s="2">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="B2326" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C2326">
-        <v>1000922411</v>
+        <v>1037603803</v>
       </c>
       <c r="D2326" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="E2326" t="s">
         <v>63</v>
@@ -61183,16 +61183,16 @@
     </row>
     <row r="2327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2327" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B2327" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C2327">
-        <v>1037603803</v>
+        <v>1026145688</v>
       </c>
       <c r="D2327" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E2327" t="s">
         <v>63</v>
@@ -61204,21 +61204,21 @@
         <v>1</v>
       </c>
       <c r="H2327">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2328" s="2">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B2328" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C2328">
-        <v>1017283114</v>
+        <v>1000922411</v>
       </c>
       <c r="D2328" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E2328" t="s">
         <v>63</v>
@@ -61235,19 +61235,19 @@
     </row>
     <row r="2329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2329" s="2">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="B2329" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C2329">
-        <v>10386260211</v>
+        <v>1037603803</v>
       </c>
       <c r="D2329" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="E2329" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2329" t="s">
         <v>67</v>
@@ -61261,19 +61261,19 @@
     </row>
     <row r="2330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2330" s="2">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B2330" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C2330">
-        <v>31274520</v>
+        <v>1017283114</v>
       </c>
       <c r="D2330" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="E2330" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2330" t="s">
         <v>67</v>
@@ -61282,24 +61282,24 @@
         <v>1</v>
       </c>
       <c r="H2330">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2331" s="2">
-        <v>46179</v>
+        <v>46177</v>
       </c>
       <c r="B2331" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C2331">
-        <v>1039679117</v>
+        <v>10386260211</v>
       </c>
       <c r="D2331" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E2331" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2331" t="s">
         <v>67</v>
@@ -61308,21 +61308,21 @@
         <v>1</v>
       </c>
       <c r="H2331">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2332" s="2">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B2332" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="C2332">
-        <v>432553771</v>
+        <v>31274520</v>
       </c>
       <c r="D2332" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="E2332" t="s">
         <v>62</v>
@@ -61339,19 +61339,19 @@
     </row>
     <row r="2333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2333" s="2">
-        <v>46183</v>
+        <v>46179</v>
       </c>
       <c r="B2333" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C2333">
-        <v>10171674991</v>
+        <v>1039679117</v>
       </c>
       <c r="D2333" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="E2333" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2333" t="s">
         <v>67</v>
@@ -61365,19 +61365,19 @@
     </row>
     <row r="2334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2334" s="2">
-        <v>46184</v>
+        <v>46175</v>
       </c>
       <c r="B2334" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C2334">
-        <v>1001547741</v>
+        <v>432553771</v>
       </c>
       <c r="D2334" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="E2334" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2334" t="s">
         <v>67</v>
@@ -61386,21 +61386,21 @@
         <v>1</v>
       </c>
       <c r="H2334">
-        <v>8.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2335" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B2335" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C2335">
-        <v>10386260211</v>
+        <v>10171674991</v>
       </c>
       <c r="D2335" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="E2335" t="s">
         <v>62</v>
@@ -61417,7 +61417,7 @@
     </row>
     <row r="2336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2336" s="2">
-        <v>46175</v>
+        <v>46184</v>
       </c>
       <c r="B2336" t="s">
         <v>46</v>
@@ -61443,71 +61443,71 @@
     </row>
     <row r="2337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2337" s="2">
-        <v>46174</v>
+        <v>46184</v>
       </c>
       <c r="B2337" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="C2337">
-        <v>1037646670</v>
+        <v>10386260211</v>
       </c>
       <c r="D2337" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E2337" t="s">
         <v>62</v>
       </c>
       <c r="F2337" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G2337">
         <v>1</v>
       </c>
       <c r="H2337">
-        <v>33.1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2338" s="2">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="B2338" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="C2338">
-        <v>1000444316</v>
+        <v>1001547741</v>
       </c>
       <c r="D2338" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E2338" t="s">
         <v>63</v>
       </c>
       <c r="F2338" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2338">
         <v>1</v>
       </c>
       <c r="H2338">
-        <v>10.17</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="2339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2339" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B2339" t="s">
         <v>81</v>
       </c>
       <c r="C2339">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2339" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2339" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2339" t="s">
         <v>68</v>
@@ -61516,12 +61516,12 @@
         <v>1</v>
       </c>
       <c r="H2339">
-        <v>16.5</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="2340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2340" s="2">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="B2340" t="s">
         <v>81</v>
@@ -61536,13 +61536,13 @@
         <v>63</v>
       </c>
       <c r="F2340" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2340">
         <v>1</v>
       </c>
       <c r="H2340">
-        <v>1</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="2341" spans="1:8" x14ac:dyDescent="0.25">
@@ -61562,18 +61562,18 @@
         <v>63</v>
       </c>
       <c r="F2341" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2341">
         <v>1</v>
       </c>
       <c r="H2341">
-        <v>3</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="2342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2342" s="2">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="B2342" t="s">
         <v>81</v>
@@ -61588,13 +61588,13 @@
         <v>63</v>
       </c>
       <c r="F2342" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2342">
         <v>1</v>
       </c>
       <c r="H2342">
-        <v>9.6999999999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2343" spans="1:8" x14ac:dyDescent="0.25">
@@ -61620,12 +61620,12 @@
         <v>1</v>
       </c>
       <c r="H2343">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2344" s="2">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B2344" t="s">
         <v>81</v>
@@ -61646,12 +61646,12 @@
         <v>1</v>
       </c>
       <c r="H2344">
-        <v>26.900000000000002</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="2345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2345" s="2">
-        <v>46183</v>
+        <v>46175</v>
       </c>
       <c r="B2345" t="s">
         <v>81</v>
@@ -61677,19 +61677,19 @@
     </row>
     <row r="2346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2346" s="2">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B2346" t="s">
         <v>81</v>
       </c>
       <c r="C2346">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2346" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2346" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2346" t="s">
         <v>68</v>
@@ -61698,12 +61698,12 @@
         <v>1</v>
       </c>
       <c r="H2346">
-        <v>24.8</v>
+        <v>26.900000000000002</v>
       </c>
     </row>
     <row r="2347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2347" s="2">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B2347" t="s">
         <v>81</v>
@@ -61729,33 +61729,33 @@
     </row>
     <row r="2348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2348" s="2">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="B2348" t="s">
         <v>81</v>
       </c>
       <c r="C2348">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2348" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2348" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2348" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2348">
         <v>1</v>
       </c>
       <c r="H2348">
-        <v>3</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="2349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2349" s="2">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B2349" t="s">
         <v>81</v>
@@ -61770,18 +61770,18 @@
         <v>63</v>
       </c>
       <c r="F2349" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G2349">
         <v>1</v>
       </c>
       <c r="H2349">
-        <v>8.85</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2350" s="2">
-        <v>46175</v>
+        <v>46179</v>
       </c>
       <c r="B2350" t="s">
         <v>81</v>
@@ -61802,50 +61802,50 @@
         <v>1</v>
       </c>
       <c r="H2350">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2351" s="2">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B2351" t="s">
         <v>81</v>
       </c>
       <c r="C2351">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2351" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2351" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2351" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2351">
         <v>1</v>
       </c>
       <c r="H2351">
-        <v>1</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="2352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2352" s="2">
-        <v>46184</v>
+        <v>46175</v>
       </c>
       <c r="B2352" t="s">
         <v>81</v>
       </c>
       <c r="C2352">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2352" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2352" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2352" t="s">
         <v>69</v>
@@ -61854,50 +61854,50 @@
         <v>1</v>
       </c>
       <c r="H2352">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2353" s="2">
-        <v>46179</v>
+        <v>46177</v>
       </c>
       <c r="B2353" t="s">
         <v>81</v>
       </c>
       <c r="C2353">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2353" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2353" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2353" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G2353">
         <v>1</v>
       </c>
       <c r="H2353">
-        <v>9.44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2354" s="2">
-        <v>46179</v>
+        <v>46184</v>
       </c>
       <c r="B2354" t="s">
         <v>81</v>
       </c>
       <c r="C2354">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2354" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2354" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2354" t="s">
         <v>69</v>
@@ -61906,12 +61906,12 @@
         <v>1</v>
       </c>
       <c r="H2354">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2355" s="2">
-        <v>46182</v>
+        <v>46179</v>
       </c>
       <c r="B2355" t="s">
         <v>81</v>
@@ -61926,18 +61926,18 @@
         <v>63</v>
       </c>
       <c r="F2355" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G2355">
         <v>1</v>
       </c>
       <c r="H2355">
-        <v>26.900000000000002</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="2356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2356" s="2">
-        <v>46183</v>
+        <v>46179</v>
       </c>
       <c r="B2356" t="s">
         <v>81</v>
@@ -61958,12 +61958,12 @@
         <v>1</v>
       </c>
       <c r="H2356">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2357" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B2357" t="s">
         <v>81</v>
@@ -61978,108 +61978,108 @@
         <v>63</v>
       </c>
       <c r="F2357" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2357">
         <v>1</v>
       </c>
       <c r="H2357">
-        <v>2</v>
+        <v>26.900000000000002</v>
       </c>
     </row>
     <row r="2358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2358" s="2">
-        <v>46178</v>
+        <v>46183</v>
       </c>
       <c r="B2358" t="s">
         <v>81</v>
       </c>
       <c r="C2358">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2358" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2358" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2358" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G2358">
         <v>1</v>
       </c>
       <c r="H2358">
-        <v>10.17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2359" s="2">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B2359" t="s">
         <v>81</v>
       </c>
       <c r="C2359">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2359" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2359" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2359" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G2359">
         <v>1</v>
       </c>
       <c r="H2359">
-        <v>10.17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2360" s="2">
-        <v>46184</v>
+        <v>46178</v>
       </c>
       <c r="B2360" t="s">
         <v>81</v>
       </c>
       <c r="C2360">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2360" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2360" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2360" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2360">
         <v>1</v>
       </c>
       <c r="H2360">
-        <v>1</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="2361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2361" s="2">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="B2361" t="s">
         <v>81</v>
       </c>
       <c r="C2361">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2361" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2361" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2361" t="s">
         <v>66</v>
@@ -62088,12 +62088,12 @@
         <v>1</v>
       </c>
       <c r="H2361">
-        <v>9.44</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="2362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2362" s="2">
-        <v>46179</v>
+        <v>46184</v>
       </c>
       <c r="B2362" t="s">
         <v>81</v>
@@ -62114,7 +62114,7 @@
         <v>1</v>
       </c>
       <c r="H2362">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2363" spans="1:8" x14ac:dyDescent="0.25">
@@ -62134,18 +62134,18 @@
         <v>63</v>
       </c>
       <c r="F2363" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2363">
         <v>1</v>
       </c>
       <c r="H2363">
-        <v>1.5</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="2364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2364" s="2">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="B2364" t="s">
         <v>81</v>
@@ -62166,12 +62166,12 @@
         <v>1</v>
       </c>
       <c r="H2364">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2365" s="2">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="B2365" t="s">
         <v>81</v>
@@ -62197,7 +62197,7 @@
     </row>
     <row r="2366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2366" s="2">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="B2366" t="s">
         <v>81</v>
@@ -62223,19 +62223,19 @@
     </row>
     <row r="2367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2367" s="2">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="B2367" t="s">
         <v>81</v>
       </c>
       <c r="C2367">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2367" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2367" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2367" t="s">
         <v>69</v>
@@ -62264,44 +62264,44 @@
         <v>63</v>
       </c>
       <c r="F2368" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2368">
         <v>1</v>
       </c>
       <c r="H2368">
-        <v>14.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2369" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B2369" t="s">
         <v>81</v>
       </c>
       <c r="C2369">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2369" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2369" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2369" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G2369">
         <v>1</v>
       </c>
       <c r="H2369">
-        <v>10.17</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2370" s="2">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B2370" t="s">
         <v>81</v>
@@ -62322,38 +62322,38 @@
         <v>1</v>
       </c>
       <c r="H2370">
-        <v>11.8</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="2371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2371" s="2">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B2371" t="s">
         <v>81</v>
       </c>
       <c r="C2371">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2371" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2371" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2371" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2371">
         <v>1</v>
       </c>
       <c r="H2371">
-        <v>2</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="2372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2372" s="2">
-        <v>46184</v>
+        <v>46176</v>
       </c>
       <c r="B2372" t="s">
         <v>81</v>
@@ -62368,13 +62368,13 @@
         <v>63</v>
       </c>
       <c r="F2372" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G2372">
         <v>1</v>
       </c>
       <c r="H2372">
-        <v>10.85</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="2373" spans="1:8" x14ac:dyDescent="0.25">
@@ -62385,13 +62385,13 @@
         <v>81</v>
       </c>
       <c r="C2373">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2373" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2373" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2373" t="s">
         <v>69</v>
@@ -62400,12 +62400,12 @@
         <v>1</v>
       </c>
       <c r="H2373">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2374" s="2">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="B2374" t="s">
         <v>81</v>
@@ -62420,13 +62420,13 @@
         <v>63</v>
       </c>
       <c r="F2374" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2374">
         <v>1</v>
       </c>
       <c r="H2374">
-        <v>1.5</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="2375" spans="1:8" x14ac:dyDescent="0.25">
@@ -62452,12 +62452,12 @@
         <v>1</v>
       </c>
       <c r="H2375">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2376" s="2">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B2376" t="s">
         <v>81</v>
@@ -62498,18 +62498,18 @@
         <v>63</v>
       </c>
       <c r="F2377" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G2377">
         <v>1</v>
       </c>
       <c r="H2377">
-        <v>9.44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2378" s="2">
-        <v>46184</v>
+        <v>46175</v>
       </c>
       <c r="B2378" t="s">
         <v>81</v>
@@ -62550,18 +62550,18 @@
         <v>63</v>
       </c>
       <c r="F2379" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2379">
         <v>1</v>
       </c>
       <c r="H2379">
-        <v>1</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="2380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2380" s="2">
-        <v>46179</v>
+        <v>46184</v>
       </c>
       <c r="B2380" t="s">
         <v>81</v>
@@ -62593,13 +62593,13 @@
         <v>81</v>
       </c>
       <c r="C2381">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2381" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2381" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2381" t="s">
         <v>69</v>
@@ -62613,7 +62613,7 @@
     </row>
     <row r="2382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2382" s="2">
-        <v>46174</v>
+        <v>46179</v>
       </c>
       <c r="B2382" t="s">
         <v>81</v>
@@ -62634,50 +62634,50 @@
         <v>1</v>
       </c>
       <c r="H2382">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2383" s="2">
-        <v>46174</v>
+        <v>46184</v>
       </c>
       <c r="B2383" t="s">
         <v>81</v>
       </c>
       <c r="C2383">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2383" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2383" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2383" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G2383">
         <v>1</v>
       </c>
       <c r="H2383">
-        <v>10.17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2384" s="2">
-        <v>46184</v>
+        <v>46174</v>
       </c>
       <c r="B2384" t="s">
         <v>81</v>
       </c>
       <c r="C2384">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2384" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2384" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2384" t="s">
         <v>69</v>
@@ -62686,12 +62686,12 @@
         <v>1</v>
       </c>
       <c r="H2384">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2385" s="2">
-        <v>46179</v>
+        <v>46174</v>
       </c>
       <c r="B2385" t="s">
         <v>81</v>
@@ -62706,30 +62706,30 @@
         <v>63</v>
       </c>
       <c r="F2385" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2385">
         <v>1</v>
       </c>
       <c r="H2385">
-        <v>1.5</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="2386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2386" s="2">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="B2386" t="s">
         <v>81</v>
       </c>
       <c r="C2386">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2386" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2386" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2386" t="s">
         <v>69</v>
@@ -62738,12 +62738,12 @@
         <v>1</v>
       </c>
       <c r="H2386">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2387" s="2">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="B2387" t="s">
         <v>81</v>
@@ -62769,7 +62769,7 @@
     </row>
     <row r="2388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2388" s="2">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B2388" t="s">
         <v>81</v>
@@ -62790,12 +62790,12 @@
         <v>1</v>
       </c>
       <c r="H2388">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2389" s="2">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="B2389" t="s">
         <v>81</v>
@@ -62816,12 +62816,12 @@
         <v>1</v>
       </c>
       <c r="H2389">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2390" s="2">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="B2390" t="s">
         <v>81</v>
@@ -62836,30 +62836,30 @@
         <v>63</v>
       </c>
       <c r="F2390" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G2390">
         <v>1</v>
       </c>
       <c r="H2390">
-        <v>10.17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2391" s="2">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="B2391" t="s">
         <v>81</v>
       </c>
       <c r="C2391">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2391" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2391" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2391" t="s">
         <v>69</v>
@@ -62873,7 +62873,7 @@
     </row>
     <row r="2392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2392" s="2">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B2392" t="s">
         <v>81</v>
@@ -62888,30 +62888,30 @@
         <v>63</v>
       </c>
       <c r="F2392" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2392">
         <v>1</v>
       </c>
       <c r="H2392">
-        <v>1</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="2393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2393" s="2">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B2393" t="s">
         <v>81</v>
       </c>
       <c r="C2393">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2393" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2393" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2393" t="s">
         <v>69</v>
@@ -62920,7 +62920,7 @@
         <v>1</v>
       </c>
       <c r="H2393">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2394" spans="1:8" x14ac:dyDescent="0.25">
@@ -62946,12 +62946,12 @@
         <v>1</v>
       </c>
       <c r="H2394">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2395" s="2">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B2395" t="s">
         <v>81</v>
@@ -62966,18 +62966,18 @@
         <v>63</v>
       </c>
       <c r="F2395" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2395">
         <v>1</v>
       </c>
       <c r="H2395">
-        <v>11.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2396" s="2">
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="B2396" t="s">
         <v>81</v>
@@ -63003,7 +63003,7 @@
     </row>
     <row r="2397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2397" s="2">
-        <v>46183</v>
+        <v>46176</v>
       </c>
       <c r="B2397" t="s">
         <v>81</v>
@@ -63024,12 +63024,12 @@
         <v>1</v>
       </c>
       <c r="H2397">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="2398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2398" s="2">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B2398" t="s">
         <v>81</v>
@@ -63044,18 +63044,18 @@
         <v>63</v>
       </c>
       <c r="F2398" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2398">
         <v>1</v>
       </c>
       <c r="H2398">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2399" s="2">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B2399" t="s">
         <v>81</v>
@@ -63076,12 +63076,12 @@
         <v>1</v>
       </c>
       <c r="H2399">
-        <v>21.8</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="2400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2400" s="2">
-        <v>46184</v>
+        <v>46177</v>
       </c>
       <c r="B2400" t="s">
         <v>81</v>
@@ -63096,18 +63096,18 @@
         <v>63</v>
       </c>
       <c r="F2400" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2400">
         <v>1</v>
       </c>
       <c r="H2400">
-        <v>2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="2401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2401" s="2">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="B2401" t="s">
         <v>81</v>
@@ -63122,18 +63122,18 @@
         <v>63</v>
       </c>
       <c r="F2401" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G2401">
         <v>1</v>
       </c>
       <c r="H2401">
-        <v>13.57</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="2402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2402" s="2">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B2402" t="s">
         <v>81</v>
@@ -63154,12 +63154,12 @@
         <v>1</v>
       </c>
       <c r="H2402">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2403" s="2">
-        <v>46184</v>
+        <v>46179</v>
       </c>
       <c r="B2403" t="s">
         <v>81</v>
@@ -63174,30 +63174,30 @@
         <v>63</v>
       </c>
       <c r="F2403" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2403">
         <v>1</v>
       </c>
       <c r="H2403">
-        <v>1.5</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="2404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2404" s="2">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="B2404" t="s">
         <v>81</v>
       </c>
       <c r="C2404">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2404" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2404" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2404" t="s">
         <v>69</v>
@@ -63211,7 +63211,7 @@
     </row>
     <row r="2405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2405" s="2">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B2405" t="s">
         <v>81</v>
@@ -63226,30 +63226,30 @@
         <v>63</v>
       </c>
       <c r="F2405" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2405">
         <v>1</v>
       </c>
       <c r="H2405">
-        <v>9</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2406" s="2">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="B2406" t="s">
         <v>81</v>
       </c>
       <c r="C2406">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2406" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2406" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2406" t="s">
         <v>69</v>
@@ -63258,12 +63258,12 @@
         <v>1</v>
       </c>
       <c r="H2406">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2407" s="2">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="B2407" t="s">
         <v>81</v>
@@ -63284,12 +63284,12 @@
         <v>1</v>
       </c>
       <c r="H2407">
-        <v>15.3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2408" s="2">
-        <v>46174</v>
+        <v>46183</v>
       </c>
       <c r="B2408" t="s">
         <v>81</v>
@@ -63304,18 +63304,18 @@
         <v>63</v>
       </c>
       <c r="F2408" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2408">
         <v>1</v>
       </c>
       <c r="H2408">
-        <v>35.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2409" s="2">
-        <v>46179</v>
+        <v>46174</v>
       </c>
       <c r="B2409" t="s">
         <v>81</v>
@@ -63330,18 +63330,18 @@
         <v>63</v>
       </c>
       <c r="F2409" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2409">
         <v>1</v>
       </c>
       <c r="H2409">
-        <v>1</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="2410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2410" s="2">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="B2410" t="s">
         <v>81</v>
@@ -63362,12 +63362,12 @@
         <v>1</v>
       </c>
       <c r="H2410">
-        <v>43</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="2411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2411" s="2">
-        <v>46183</v>
+        <v>46179</v>
       </c>
       <c r="B2411" t="s">
         <v>81</v>
@@ -63393,7 +63393,7 @@
     </row>
     <row r="2412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2412" s="2">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="B2412" t="s">
         <v>81</v>
@@ -63414,12 +63414,12 @@
         <v>1</v>
       </c>
       <c r="H2412">
-        <v>13.7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2413" s="2">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B2413" t="s">
         <v>81</v>
@@ -63445,7 +63445,7 @@
     </row>
     <row r="2414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2414" s="2">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="B2414" t="s">
         <v>81</v>
@@ -63460,56 +63460,56 @@
         <v>63</v>
       </c>
       <c r="F2414" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2414">
         <v>1</v>
       </c>
       <c r="H2414">
-        <v>3</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="2415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2415" s="2">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B2415" t="s">
         <v>81</v>
       </c>
       <c r="C2415">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2415" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2415" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2415" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2415">
         <v>1</v>
       </c>
       <c r="H2415">
-        <v>11.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2416" s="2">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B2416" t="s">
         <v>81</v>
       </c>
       <c r="C2416">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2416" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2416" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2416" t="s">
         <v>69</v>
@@ -63518,7 +63518,7 @@
         <v>1</v>
       </c>
       <c r="H2416">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2417" spans="1:8" x14ac:dyDescent="0.25">
@@ -63529,13 +63529,13 @@
         <v>81</v>
       </c>
       <c r="C2417">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2417" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2417" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2417" t="s">
         <v>68</v>
@@ -63544,12 +63544,12 @@
         <v>1</v>
       </c>
       <c r="H2417">
-        <v>22.400000000000002</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="2418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2418" s="2">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B2418" t="s">
         <v>81</v>
@@ -63596,24 +63596,24 @@
         <v>1</v>
       </c>
       <c r="H2419">
-        <v>13.9</v>
+        <v>22.400000000000002</v>
       </c>
     </row>
     <row r="2420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2420" s="2">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="B2420" t="s">
         <v>81</v>
       </c>
       <c r="C2420">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2420" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2420" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2420" t="s">
         <v>69</v>
@@ -63622,12 +63622,12 @@
         <v>1</v>
       </c>
       <c r="H2420">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2421" s="2">
-        <v>46184</v>
+        <v>46178</v>
       </c>
       <c r="B2421" t="s">
         <v>81</v>
@@ -63648,24 +63648,24 @@
         <v>1</v>
       </c>
       <c r="H2421">
-        <v>22.400000000000002</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="2422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2422" s="2">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B2422" t="s">
         <v>81</v>
       </c>
       <c r="C2422">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2422" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2422" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2422" t="s">
         <v>69</v>
@@ -63674,12 +63674,12 @@
         <v>1</v>
       </c>
       <c r="H2422">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2423" s="2">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="B2423" t="s">
         <v>81</v>
@@ -63700,7 +63700,7 @@
         <v>1</v>
       </c>
       <c r="H2423">
-        <v>16.3</v>
+        <v>22.400000000000002</v>
       </c>
     </row>
     <row r="2424" spans="1:8" x14ac:dyDescent="0.25">
@@ -63711,13 +63711,13 @@
         <v>81</v>
       </c>
       <c r="C2424">
-        <v>1000444316</v>
+        <v>1037646670</v>
       </c>
       <c r="D2424" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E2424" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2424" t="s">
         <v>69</v>
@@ -63726,12 +63726,12 @@
         <v>1</v>
       </c>
       <c r="H2424">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2425" s="2">
-        <v>46184</v>
+        <v>46177</v>
       </c>
       <c r="B2425" t="s">
         <v>81</v>
@@ -63752,24 +63752,24 @@
         <v>1</v>
       </c>
       <c r="H2425">
-        <v>13.9</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="2426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2426" s="2">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="B2426" t="s">
         <v>81</v>
       </c>
       <c r="C2426">
-        <v>1037646670</v>
+        <v>1000444316</v>
       </c>
       <c r="D2426" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2426" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2426" t="s">
         <v>69</v>
@@ -63778,12 +63778,12 @@
         <v>1</v>
       </c>
       <c r="H2426">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="2427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2427" s="2">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B2427" t="s">
         <v>81</v>
@@ -63798,70 +63798,70 @@
         <v>63</v>
       </c>
       <c r="F2427" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2427">
         <v>1</v>
       </c>
       <c r="H2427">
-        <v>21</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="2428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2428" s="2">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="B2428" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C2428">
-        <v>98667259</v>
+        <v>1037646670</v>
       </c>
       <c r="D2428" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E2428" t="s">
         <v>62</v>
       </c>
       <c r="F2428" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G2428">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="H2428">
-        <v>1093.1500000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2429" s="2">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="B2429" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C2429">
-        <v>98667259</v>
+        <v>1000444316</v>
       </c>
       <c r="D2429" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E2429" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2429" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G2429">
-        <v>1368</v>
+        <v>1</v>
       </c>
       <c r="H2429">
-        <v>2395.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2430" s="2">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B2430" t="s">
         <v>73</v>
@@ -63876,13 +63876,13 @@
         <v>62</v>
       </c>
       <c r="F2430" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2430">
-        <v>354</v>
+        <v>56</v>
       </c>
       <c r="H2430">
-        <v>3830.6600000000112</v>
+        <v>1093.1500000000001</v>
       </c>
     </row>
     <row r="2431" spans="1:8" x14ac:dyDescent="0.25">
@@ -63902,372 +63902,416 @@
         <v>62</v>
       </c>
       <c r="F2431" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2431">
-        <v>568</v>
+        <v>1368</v>
       </c>
       <c r="H2431">
-        <v>10296.09999999998</v>
+        <v>2395.5</v>
       </c>
     </row>
     <row r="2432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2432" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B2432" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2432">
+        <v>98667259</v>
+      </c>
+      <c r="D2432" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2432" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2432" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2432">
+        <v>354</v>
+      </c>
+      <c r="H2432">
+        <v>3830.6600000000112</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2433" s="2">
         <v>46175</v>
       </c>
-      <c r="B2432" t="s">
+      <c r="B2433" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2433">
+        <v>98667259</v>
+      </c>
+      <c r="D2433" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2433" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2433" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2433">
+        <v>568</v>
+      </c>
+      <c r="H2433">
+        <v>10296.09999999998</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2434" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B2434" t="s">
         <v>15</v>
-      </c>
-      <c r="F2432" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2432">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="2433" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2433" s="2">
-        <v>46174</v>
-      </c>
-      <c r="B2433" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2433" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2433">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="2434" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2434" s="2">
-        <v>46174</v>
-      </c>
-      <c r="B2434" t="s">
-        <v>7</v>
       </c>
       <c r="F2434" t="s">
         <v>78</v>
       </c>
       <c r="G2434">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2435" spans="1:7" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2435" s="2">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B2435" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2435" t="s">
         <v>78</v>
       </c>
       <c r="G2435">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="2436" spans="1:7" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2436" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B2436" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F2436" t="s">
         <v>78</v>
       </c>
       <c r="G2436">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="2437" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2437" s="2">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B2437" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F2437" t="s">
         <v>78</v>
       </c>
       <c r="G2437">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="2438" spans="1:7" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2438" s="2">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B2438" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F2438" t="s">
         <v>78</v>
       </c>
       <c r="G2438">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="2439" spans="1:7" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2439" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B2439" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F2439" t="s">
         <v>78</v>
       </c>
       <c r="G2439">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="2440" spans="1:7" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2440" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B2440" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F2440" t="s">
         <v>78</v>
       </c>
       <c r="G2440">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="2441" spans="1:7" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2441" s="2">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B2441" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F2441" t="s">
         <v>78</v>
       </c>
       <c r="G2441">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="2442" spans="1:7" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2442" s="2">
         <v>46175</v>
       </c>
       <c r="B2442" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="F2442" t="s">
         <v>78</v>
       </c>
       <c r="G2442">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="2443" spans="1:7" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2443" s="2">
         <v>46176</v>
       </c>
       <c r="B2443" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="F2443" t="s">
         <v>78</v>
       </c>
       <c r="G2443">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2444" spans="1:7" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2444" s="2">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B2444" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F2444" t="s">
         <v>78</v>
       </c>
       <c r="G2444">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="2445" spans="1:7" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2445" s="2">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B2445" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F2445" t="s">
         <v>78</v>
       </c>
       <c r="G2445">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="2446" spans="1:7" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2446" s="2">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B2446" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F2446" t="s">
         <v>78</v>
       </c>
       <c r="G2446">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="2447" spans="1:7" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2447" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B2447" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="F2447" t="s">
         <v>78</v>
       </c>
       <c r="G2447">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2448" spans="1:7" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2448" s="2">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B2448" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F2448" t="s">
         <v>78</v>
       </c>
       <c r="G2448">
-        <v>383</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2449" s="2">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B2449" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F2449" t="s">
         <v>78</v>
       </c>
       <c r="G2449">
-        <v>373</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2450" s="2">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B2450" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F2450" t="s">
         <v>78</v>
       </c>
       <c r="G2450">
-        <v>392</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2451" s="2">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B2451" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F2451" t="s">
         <v>78</v>
       </c>
       <c r="G2451">
-        <v>620</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2452" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B2452" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F2452" t="s">
         <v>78</v>
       </c>
       <c r="G2452">
-        <v>294</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2453" s="2">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B2453" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F2453" t="s">
         <v>78</v>
       </c>
       <c r="G2453">
-        <v>362</v>
+        <v>620</v>
       </c>
     </row>
     <row r="2454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2454" s="2">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B2454" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F2454" t="s">
         <v>78</v>
       </c>
       <c r="G2454">
-        <v>6766</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2455" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B2455" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="F2455" t="s">
         <v>78</v>
       </c>
       <c r="G2455">
-        <v>0</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2456" s="2">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B2456" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="F2456" t="s">
         <v>78</v>
       </c>
       <c r="G2456">
+        <v>6766</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2457" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B2457" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2457" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2457">
         <v>0</v>
       </c>
     </row>
-    <row r="2457" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2457" s="2"/>
-      <c r="G2457"/>
-    </row>
     <row r="2458" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2458" s="2"/>
-      <c r="G2458"/>
+      <c r="A2458" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B2458" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2458" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2458">
+        <v>0</v>
+      </c>
     </row>
     <row r="2459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2459" s="2"/>
@@ -66313,7 +66357,7 @@
       <c r="A2969" s="2"/>
       <c r="G2969"/>
     </row>
-    <row r="2970" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2970" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2970" s="2"/>
       <c r="G2970"/>
     </row>
@@ -66321,7 +66365,7 @@
       <c r="A2971" s="2"/>
       <c r="G2971"/>
     </row>
-    <row r="2972" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2972" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2972" s="2"/>
       <c r="G2972"/>
     </row>
@@ -79691,20 +79735,20 @@
     </row>
     <row r="6314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6314" s="2"/>
+      <c r="G6314"/>
     </row>
     <row r="6315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6315" s="2"/>
+      <c r="G6315"/>
     </row>
     <row r="6316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6316" s="2"/>
     </row>
     <row r="6317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6317" s="2"/>
-      <c r="G6317"/>
     </row>
     <row r="6318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6318" s="2"/>
-      <c r="G6318"/>
     </row>
     <row r="6319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6319" s="2"/>
@@ -79800,9 +79844,11 @@
     </row>
     <row r="6342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6342" s="2"/>
+      <c r="G6342"/>
     </row>
     <row r="6343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6343" s="2"/>
+      <c r="G6343"/>
     </row>
     <row r="6344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6344" s="2"/>
@@ -79828,8 +79874,14 @@
     <row r="6351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6351" s="2"/>
     </row>
+    <row r="6352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6352" s="2"/>
+    </row>
+    <row r="6353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6353" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H6341" xr:uid="{14AE435F-C8B7-4B0C-8617-5994DE6D3EA0}"/>
+  <autoFilter ref="A1:H6343" xr:uid="{14AE435F-C8B7-4B0C-8617-5994DE6D3EA0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
